--- a/ValueSet-onconova-vs-cancer-risk-assessment-values.xlsx
+++ b/ValueSet-onconova-vs-cancer-risk-assessment-values.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-25T15:12:31+00:00</t>
+    <t>2026-03-18T14:24:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-onconova-vs-cancer-risk-assessment-values.xlsx
+++ b/ValueSet-onconova-vs-cancer-risk-assessment-values.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T14:24:59+00:00</t>
+    <t>2026-03-31T06:24:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-onconova-vs-cancer-risk-assessment-values.xlsx
+++ b/ValueSet-onconova-vs-cancer-risk-assessment-values.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>1.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T06:24:20+00:00</t>
+    <t>2026-04-09T04:48:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-onconova-vs-cancer-risk-assessment-values.xlsx
+++ b/ValueSet-onconova-vs-cancer-risk-assessment-values.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-09T04:48:36+00:00</t>
+    <t>2026-04-15T07:47:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-onconova-vs-cancer-risk-assessment-values.xlsx
+++ b/ValueSet-onconova-vs-cancer-risk-assessment-values.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T07:47:05+00:00</t>
+    <t>2026-04-15T19:05:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-onconova-vs-cancer-risk-assessment-values.xlsx
+++ b/ValueSet-onconova-vs-cancer-risk-assessment-values.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="102">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T19:05:31+00:00</t>
+    <t>2026-04-16T05:59:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -201,88 +201,16 @@
     <t>Child-Pugh Class A</t>
   </si>
   <si>
-    <t>C146790</t>
-  </si>
-  <si>
-    <t>Child-Pugh Class A5</t>
-  </si>
-  <si>
-    <t>C146791</t>
-  </si>
-  <si>
-    <t>Child-Pugh Class A6</t>
-  </si>
-  <si>
     <t>C113692</t>
   </si>
   <si>
     <t>Child-Pugh Class B</t>
   </si>
   <si>
-    <t>C146792</t>
-  </si>
-  <si>
-    <t>Child-Pugh Class B7</t>
-  </si>
-  <si>
-    <t>C146793</t>
-  </si>
-  <si>
-    <t>Child-Pugh Class B8</t>
-  </si>
-  <si>
-    <t>C146794</t>
-  </si>
-  <si>
-    <t>Child-Pugh Class B9</t>
-  </si>
-  <si>
     <t>C113694</t>
   </si>
   <si>
     <t>Child-Pugh Class C</t>
-  </si>
-  <si>
-    <t>C146795</t>
-  </si>
-  <si>
-    <t>Child-Pugh Class C10</t>
-  </si>
-  <si>
-    <t>C146796</t>
-  </si>
-  <si>
-    <t>Child-Pugh Class C11</t>
-  </si>
-  <si>
-    <t>C146797</t>
-  </si>
-  <si>
-    <t>Child-Pugh Class C12</t>
-  </si>
-  <si>
-    <t>C146798</t>
-  </si>
-  <si>
-    <t>Child-Pugh Class C13</t>
-  </si>
-  <si>
-    <t>C146799</t>
-  </si>
-  <si>
-    <t>Child-Pugh Class C14</t>
-  </si>
-  <si>
-    <t>C146801</t>
-  </si>
-  <si>
-    <t>Child-Pugh Class C15</t>
-  </si>
-  <si>
-    <t>C148151</t>
-  </si>
-  <si>
-    <t>Child-Pugh A-B7 Cirrhosis</t>
   </si>
   <si>
     <t>C192873</t>
@@ -652,7 +580,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B51"/>
+  <dimension ref="A1:B39"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -957,114 +885,18 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>101</v>
+        <v>20</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="B40" t="s" s="2">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="B41" t="s" s="2">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="B42" t="s" s="2">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="B43" t="s" s="2">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="B44" t="s" s="2">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="B45" t="s" s="2">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="B46" t="s" s="2">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="B47" t="s" s="2">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="B48" t="s" s="2">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="B49" t="s" s="2">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="B50" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="B51" t="s" s="2">
-        <v>125</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/ValueSet-onconova-vs-cancer-risk-assessment-values.xlsx
+++ b/ValueSet-onconova-vs-cancer-risk-assessment-values.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.0</t>
+    <t>1.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T05:59:15+00:00</t>
+    <t>2026-04-26T18:09:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
